--- a/outputs/tables/tabla_06_breakeven.xlsx
+++ b/outputs/tables/tabla_06_breakeven.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="breakeven" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,32 +429,42 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>breakeven_mtl</t>
+          <t>ruta</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>riesgo_mtl</t>
+          <t>breakeven</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>colchon_pct_mtl</t>
+          <t>breakeven_min</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>breakeven_yvr</t>
+          <t>breakeven_max</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>riesgo_yvr</t>
+          <t>riesgo_puntual</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>colchon_pct_yvr</t>
+          <t>riesgo_robusto</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>grado</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>colchon_vs_spot_pct</t>
         </is>
       </c>
     </row>
@@ -469,333 +479,873 @@
           <t>0901.11.90.00</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>1911.516195250935</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Verde</t>
-        </is>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CTG-Montreal</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1460.41772431701</v>
       </c>
       <c r="E2" t="n">
-        <v>38.25025936088173</v>
+        <v>1134.667586752987</v>
       </c>
       <c r="F2" t="n">
-        <v>2130.903177942038</v>
+        <v>1751.392792729317</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Verde</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>31.16316833103255</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>34.90521191386744</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Carbón bituminoso</t>
+          <t>Café sin tostar</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2701.12.00.00</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>3826.977747195427</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Rojo</t>
-        </is>
+          <t>0901.11.90.00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CTG-Vancouver</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1460.41772431701</v>
       </c>
       <c r="E3" t="n">
-        <v>-23.62693233157378</v>
+        <v>1134.667586752987</v>
       </c>
       <c r="F3" t="n">
-        <v>11804.68620869007</v>
+        <v>1751.392792729317</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rojo</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>-281.3393334169984</v>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>34.90521191386744</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Frutas tropicales (guayaba/mango)</t>
+          <t>Carbón bituminoso</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0804.50.00.00</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2001.790732831867</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Verde</t>
-        </is>
+          <t>2701.12.00.00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CTG-Montreal</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2192.811618419759</v>
       </c>
       <c r="E4" t="n">
-        <v>35.33402496235126</v>
+        <v>1757.474017704071</v>
       </c>
       <c r="F4" t="n">
-        <v>2586.822686674808</v>
+        <v>2496.59860458896</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Verde</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>16.43511554942013</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>2.260425057085106</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Flores frescas otras (pompones/hortensias)</t>
+          <t>Carbón bituminoso</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0603.19.00.00</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1926.682317564532</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Verde</t>
-        </is>
+          <t>2701.12.00.00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CTG-Vancouver</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2192.811618419759</v>
       </c>
       <c r="E5" t="n">
-        <v>37.76033198192862</v>
+        <v>1757.474017704071</v>
       </c>
       <c r="F5" t="n">
-        <v>2207.497655409143</v>
+        <v>2496.59860458896</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Verde</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>28.68885546372167</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>2.260425057085106</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Medicamentos corticosteroides</t>
+          <t>Frutas tropicales (guayaba/mango)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3004.32.00.00</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1863.541726707926</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Verde</t>
-        </is>
+          <t>0804.50.00.00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CTG-Montreal</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1809.164429989485</v>
       </c>
       <c r="E6" t="n">
-        <v>39.80002964124363</v>
+        <v>1505.224805751252</v>
       </c>
       <c r="F6" t="n">
-        <v>1888.614524729767</v>
+        <v>2139.533586770174</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Verde</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>38.99007638068942</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>19.36062318182952</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Medias/calcetines fibra sintética</t>
+          <t>Frutas tropicales (guayaba/mango)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6115.96.00.00</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1882.840753901698</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Verde</t>
-        </is>
+          <t>0804.50.00.00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CTG-Vancouver</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1809.164429989485</v>
       </c>
       <c r="E7" t="n">
-        <v>39.17659264041493</v>
+        <v>1505.224805751252</v>
       </c>
       <c r="F7" t="n">
-        <v>1986.081686932805</v>
+        <v>2139.533586770174</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Verde</t>
         </is>
       </c>
-      <c r="H7" t="n">
-        <v>35.84149097930944</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>19.36062318182952</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Accesorios tubería hierro/acero</t>
+          <t>Flores frescas otras (pompones/hortensias)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7307.92.00.00</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>1939.888192776371</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Verde</t>
-        </is>
+          <t>0603.19.00.00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CTG-Montreal</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2209.084988197687</v>
       </c>
       <c r="E8" t="n">
-        <v>37.33372854991502</v>
+        <v>1970.834442882163</v>
       </c>
       <c r="F8" t="n">
-        <v>2274.192166400909</v>
+        <v>2425.258262904824</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Verde</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>26.53435174252579</v>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1.535076727286561</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Filetes de trucha congelados</t>
+          <t>Flores frescas otras (pompones/hortensias)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0304.82.00.00</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1888.865493094266</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Verde</t>
-        </is>
+          <t>0603.19.00.00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CTG-Vancouver</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2209.084988197687</v>
       </c>
       <c r="E9" t="n">
-        <v>38.98196908269482</v>
+        <v>1970.834442882163</v>
       </c>
       <c r="F9" t="n">
-        <v>2016.50882847818</v>
+        <v>2425.258262904824</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Verde</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>34.85857066532802</v>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1.535076727286561</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nueces y semillas preparadas</t>
+          <t>Medicamentos corticosteroides</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2008.19.00.00</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1897.660103436188</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Verde</t>
-        </is>
+          <t>3004.32.00.00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CTG-Montreal</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>812.9692076888922</v>
       </c>
       <c r="E10" t="n">
-        <v>38.69786743135384</v>
+        <v>507.0942635882936</v>
       </c>
       <c r="F10" t="n">
-        <v>2060.924834741195</v>
+        <v>1240.569894849932</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Verde</t>
         </is>
       </c>
-      <c r="H10" t="n">
-        <v>33.42375317658235</v>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>63.76375237447317</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Medicamentos corticosteroides</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3004.32.00.00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CTG-Vancouver</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>812.9692076888922</v>
+      </c>
+      <c r="E11" t="n">
+        <v>507.0942635882936</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1240.569894849932</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>63.76375237447317</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Medias/calcetines fibra sintética</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>6115.96.00.00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CTG-Montreal</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1535.724070576311</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1235.290874020784</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1853.321017002531</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>31.54860334245155</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Medias/calcetines fibra sintética</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>6115.96.00.00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CTG-Vancouver</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1535.724070576311</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1235.290874020784</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1853.321017002531</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>31.54860334245155</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Accesorios tubería hierro/acero</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>7307.92.00.00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CTG-Montreal</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1869.730143589406</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1567.035656652546</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2209.176743611347</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>16.66104468012651</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Accesorios tubería hierro/acero</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7307.92.00.00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CTG-Vancouver</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1869.730143589406</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1567.035656652546</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2209.176743611347</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>16.66104468012651</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Filetes de trucha congelados</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0304.82.00.00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CTG-Montreal</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1727.806454923217</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1395.641131706174</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2082.242717400851</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>22.98696930039113</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Filetes de trucha congelados</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0304.82.00.00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CTG-Vancouver</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1727.806454923217</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1395.641131706174</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2082.242717400851</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>22.98696930039113</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Nueces y semillas preparadas</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2008.19.00.00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CTG-Montreal</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1897.043421602661</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1572.553387837943</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2233.025810729878</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>15.4436176285328</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Nueces y semillas preparadas</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2008.19.00.00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CTG-Vancouver</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1897.043421602661</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1572.553387837943</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2233.025810729878</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>15.4436176285328</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Rosas frescas cortadas</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>0603.11.00.00</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>1919.254012757872</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Verde</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>38.00029641243626</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2169.981992976276</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Verde</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>29.90076380689434</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CTG-Montreal</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2209.084988197687</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1970.834442882162</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2425.258262904823</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>1.535076727286581</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Rosas frescas cortadas</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0603.11.00.00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CTG-Vancouver</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2209.084988197687</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1970.834442882162</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2425.258262904823</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>1.535076727286581</v>
       </c>
     </row>
   </sheetData>
